--- a/Zinc/5. Cluster analysis/Typology2 Plots/Sites_by_typology.xlsx
+++ b/Zinc/5. Cluster analysis/Typology2 Plots/Sites_by_typology.xlsx
@@ -1,174 +1,167 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/5. Cluster analysis/Typology2 Plots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_83CD9D582E65A6403CBD34F048E41DA392D5BDBC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A819E4AE-E217-422C-B04B-2FA82C09DC30}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="NP Tribs" sheetId="1" r:id="rId1"/>
-    <sheet name="PD Tribs" sheetId="2" r:id="rId2"/>
+    <sheet name="NP Tribs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PD Tribs" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>Typology2</t>
-  </si>
-  <si>
-    <t>MTN4</t>
-  </si>
-  <si>
-    <t>Non-Perennial</t>
-  </si>
-  <si>
-    <t>MCA3.3</t>
-  </si>
-  <si>
-    <t>MCA3.2</t>
-  </si>
-  <si>
-    <t>MCA4</t>
-  </si>
-  <si>
-    <t>MCA2</t>
-  </si>
-  <si>
-    <t>MCA3.1</t>
-  </si>
-  <si>
-    <t>WBK2</t>
-  </si>
-  <si>
-    <t>WBK3</t>
-  </si>
-  <si>
-    <t>BSL5.1</t>
-  </si>
-  <si>
-    <t>NBO3</t>
-  </si>
-  <si>
-    <t>BSL8</t>
-  </si>
-  <si>
-    <t>NBO5</t>
-  </si>
-  <si>
-    <t>MTN1.1</t>
-  </si>
-  <si>
-    <t>Perennial Developed</t>
-  </si>
-  <si>
-    <t>EFK13.8</t>
-  </si>
-  <si>
-    <t>MCA1</t>
-  </si>
-  <si>
-    <t>EFK16.2</t>
-  </si>
-  <si>
-    <t>WBK1</t>
-  </si>
-  <si>
-    <t>Downtown</t>
-  </si>
-  <si>
-    <t>BSL1.1</t>
-  </si>
-  <si>
-    <t>BSL1.3</t>
-  </si>
-  <si>
-    <t>BSL1.2</t>
-  </si>
-  <si>
-    <t>BSL2.1</t>
-  </si>
-  <si>
-    <t>BSL2.2</t>
-  </si>
-  <si>
-    <t>BSL2.3</t>
-  </si>
-  <si>
-    <t>BSL3.1</t>
-  </si>
-  <si>
-    <t>BSL3.2</t>
-  </si>
-  <si>
-    <t>BSL3.3</t>
-  </si>
-  <si>
-    <t>EFK23.5</t>
-  </si>
-  <si>
-    <t>EFK18.2</t>
-  </si>
-  <si>
-    <t>Mill Branch</t>
-  </si>
-  <si>
-    <t>EFK11.3</t>
-  </si>
-  <si>
-    <t>EFK10.0</t>
-  </si>
-  <si>
-    <t>Gum Hollow</t>
-  </si>
-  <si>
-    <t>Pinhook Branch</t>
-  </si>
-  <si>
-    <t>EFK7.9</t>
-  </si>
-  <si>
-    <t>EFK5.4</t>
-  </si>
-  <si>
-    <t>BCK0.9</t>
-  </si>
-  <si>
-    <t>EFK2.0</t>
-  </si>
-  <si>
-    <t>NBO2</t>
-  </si>
-  <si>
-    <t>EFK20</t>
-  </si>
-  <si>
-    <t>BSL4.1</t>
-  </si>
-  <si>
-    <t>BSL4.2</t>
-  </si>
-  <si>
-    <t>BSL4.3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+  <si>
+    <t xml:space="preserve">Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typology2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTN1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Developed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK13.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK16.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downtown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK23.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK18.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mill Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK11.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK10.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gum Hollow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinhook Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK7.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCK0.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFK20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -204,15 +197,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -494,14 +478,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -517,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -525,7 +506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -533,7 +514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -541,7 +522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -549,7 +530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -557,7 +538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -565,7 +546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -573,7 +554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -581,7 +562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -589,7 +570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -597,7 +578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -607,19 +588,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -627,7 +605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -635,7 +613,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -643,7 +621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -651,7 +629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -659,7 +637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -667,7 +645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -675,7 +653,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -683,7 +661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -691,7 +669,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -699,7 +677,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -707,7 +685,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -715,7 +693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -723,7 +701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -731,7 +709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -739,7 +717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -747,7 +725,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -755,7 +733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -763,7 +741,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -771,7 +749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -779,7 +757,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -787,7 +765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -795,7 +773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -803,7 +781,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -811,7 +789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -819,7 +797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -827,7 +805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -835,7 +813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -843,7 +821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -851,7 +829,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -859,7 +837,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -867,7 +845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -877,6 +855,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>